--- a/grupos/1EM - Estadisticos 20221.xlsx
+++ b/grupos/1EM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="184">
   <si>
     <t>Materia</t>
   </si>
@@ -212,12 +212,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
@@ -245,43 +245,184 @@
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MAY</t>
+  </si>
+  <si>
+    <t>NEPOMUCENO</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VIDERIQUE</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>TOBIAS</t>
+  </si>
+  <si>
+    <t>LEONOR</t>
+  </si>
+  <si>
+    <t>ESTEFANY CELESTE</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>GUSTAVO KALEL</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>FLORENTINA ESMERALDA</t>
+  </si>
+  <si>
+    <t>GABRIELA AIMEE</t>
+  </si>
+  <si>
+    <t>DYLAN NAHIM</t>
+  </si>
+  <si>
+    <t>ERICK</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>BELEN</t>
+  </si>
+  <si>
+    <t>ESTEFANY VIANEY</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>ACSA FERNANDA</t>
+  </si>
+  <si>
+    <t>NERY JOSELYN</t>
+  </si>
+  <si>
     <t>ARZATE</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
+    <t>APONTE</t>
   </si>
   <si>
     <t>CABRERA</t>
   </si>
   <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MAY</t>
+    <t>MARCIAL</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MENCIAS</t>
   </si>
   <si>
     <t>MORALES</t>
@@ -290,49 +431,25 @@
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>NEPOMUCENO</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
     <t>PLIEGO</t>
   </si>
   <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
+    <t>ROSETE</t>
   </si>
   <si>
     <t>TENORIO</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>VIÑAS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
   </si>
   <si>
     <t>OJEDA</t>
@@ -341,16 +458,19 @@
     <t>ZEPACTLE</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
+    <t>MONTALVO</t>
   </si>
   <si>
     <t>MIXCOHA</t>
   </si>
   <si>
-    <t>SERRANO</t>
+    <t>ACAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>LINARES</t>
@@ -359,76 +479,64 @@
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>MONTIEL</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VIDERIQUE</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
     <t>SALAS</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>TOBIAS</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>APALE</t>
   </si>
   <si>
     <t>LUCIANA</t>
   </si>
   <si>
-    <t>LEONOR</t>
-  </si>
-  <si>
-    <t>ESTEFANY CELESTE</t>
+    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>DARA NAOMI</t>
   </si>
   <si>
+    <t>MAYRA</t>
+  </si>
+  <si>
+    <t>JULIANA</t>
+  </si>
+  <si>
+    <t>KARENT LILIANA</t>
+  </si>
+  <si>
     <t>ABIGAIL ANTONIA</t>
   </si>
   <si>
     <t>ABRIL</t>
   </si>
   <si>
-    <t>XIMENA</t>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>MARIA MONTSERRAT</t>
   </si>
   <si>
     <t>DANNA ANGELA</t>
   </si>
   <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>GUSTAVO KALEL</t>
-  </si>
-  <si>
     <t>ILSE MARIA</t>
   </si>
   <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>FLORENTINA ESMERALDA</t>
-  </si>
-  <si>
-    <t>GABRIELA AIMEE</t>
+    <t>ALANIS YUMEI</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>FELIX RAFAEL</t>
   </si>
   <si>
     <t>JOSELYN</t>
@@ -437,130 +545,22 @@
     <t>ZURI GABRIELA</t>
   </si>
   <si>
-    <t>DYLAN NAHIM</t>
-  </si>
-  <si>
-    <t>ERICK</t>
-  </si>
-  <si>
     <t>ODALIS SOFIA</t>
   </si>
   <si>
     <t>JESUS ADRIAN</t>
   </si>
   <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>BELEN</t>
-  </si>
-  <si>
-    <t>ESTEFANY VIANEY</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
+    <t>AZUL ARIADNA</t>
   </si>
   <si>
     <t>ORESTES</t>
   </si>
   <si>
-    <t>ACSA FERNANDA</t>
-  </si>
-  <si>
     <t>MELISA VIANNEY</t>
   </si>
   <si>
     <t>ARACELY</t>
-  </si>
-  <si>
-    <t>NERY JOSELYN</t>
-  </si>
-  <si>
-    <t>APONTE</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MARCIAL</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MENCIAS</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>VIÑAS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>ACAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MAYRA</t>
-  </si>
-  <si>
-    <t>JULIANA</t>
-  </si>
-  <si>
-    <t>KARENT LILIANA</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
-    <t>MARIA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>ALANIS YUMEI</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>FELIX RAFAEL</t>
-  </si>
-  <si>
-    <t>AZUL ARIADNA</t>
   </si>
   <si>
     <t>REYNA LINDA</t>
@@ -1061,7 +1061,7 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>6</v>
@@ -1115,7 +1115,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>6</v>
@@ -1292,7 +1292,7 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E7">
         <v>9</v>
@@ -1346,7 +1346,7 @@
         <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1369,7 +1369,7 @@
         <v>8</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E8">
         <v>9</v>
@@ -1423,7 +1423,7 @@
         <v>8</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1446,7 +1446,7 @@
         <v>10</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>6</v>
@@ -1500,7 +1500,7 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -1754,7 +1754,7 @@
         <v>10</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E13">
         <v>8</v>
@@ -1808,7 +1808,7 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1831,7 +1831,7 @@
         <v>10</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -1885,7 +1885,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1908,7 +1908,7 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>6</v>
@@ -1962,7 +1962,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -1985,7 +1985,7 @@
         <v>8</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -2039,7 +2039,7 @@
         <v>8</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -2216,7 +2216,7 @@
         <v>10</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>8</v>
@@ -2270,7 +2270,7 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2678,7 +2678,7 @@
         <v>8</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E25">
         <v>7</v>
@@ -2732,7 +2732,7 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W25">
         <v>7</v>
@@ -2909,7 +2909,7 @@
         <v>10</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E28">
         <v>9</v>
@@ -2963,7 +2963,7 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2986,7 +2986,7 @@
         <v>9</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E29">
         <v>6</v>
@@ -3040,7 +3040,7 @@
         <v>9</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>6</v>
@@ -3140,7 +3140,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E31">
         <v>6</v>
@@ -3194,7 +3194,7 @@
         <v>7</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -3217,7 +3217,7 @@
         <v>10</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -3271,7 +3271,7 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>6</v>
@@ -3371,7 +3371,7 @@
         <v>10</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E34">
         <v>8</v>
@@ -3425,7 +3425,7 @@
         <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>8</v>
@@ -3448,7 +3448,7 @@
         <v>9</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E35">
         <v>6</v>
@@ -3502,7 +3502,7 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W35">
         <v>6</v>
@@ -3525,7 +3525,7 @@
         <v>5</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E36">
         <v>5</v>
@@ -3579,7 +3579,7 @@
         <v>5</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W36">
         <v>5</v>
@@ -3679,7 +3679,7 @@
         <v>7</v>
       </c>
       <c r="D38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E38">
         <v>7</v>
@@ -3733,7 +3733,7 @@
         <v>7</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W38">
         <v>7</v>
@@ -3756,7 +3756,7 @@
         <v>10</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E39">
         <v>8</v>
@@ -3810,7 +3810,7 @@
         <v>10</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W39">
         <v>8</v>
@@ -3910,7 +3910,7 @@
         <v>10</v>
       </c>
       <c r="D41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E41">
         <v>8</v>
@@ -3964,7 +3964,7 @@
         <v>10</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W41">
         <v>8</v>
@@ -3987,7 +3987,7 @@
         <v>10</v>
       </c>
       <c r="D42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E42">
         <v>6</v>
@@ -4041,7 +4041,7 @@
         <v>10</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W42">
         <v>6</v>
@@ -4064,7 +4064,7 @@
         <v>10</v>
       </c>
       <c r="D43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E43">
         <v>9</v>
@@ -4118,7 +4118,7 @@
         <v>10</v>
       </c>
       <c r="V43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W43">
         <v>9</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -4423,30 +4423,30 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>34.88</v>
+        <v>60.47</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="I2">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J2">
-        <v>65.12</v>
+        <v>39.53</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -4455,25 +4455,25 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>60.47</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>6.98</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>39.53</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4611,7 +4611,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4646,13 +4646,13 @@
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>64</v>
@@ -4660,39 +4660,39 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920124</v>
+        <v>22330051920342</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920343</v>
+        <v>22330051920126</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>64</v>
@@ -4700,99 +4700,99 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920342</v>
+        <v>22330051920132</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920126</v>
+        <v>22330051920244</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920126</v>
+        <v>22330051920244</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920344</v>
+        <v>22330051920346</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920130</v>
+        <v>22330051920346</v>
       </c>
       <c r="B9" t="s">
         <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>64</v>
@@ -4800,39 +4800,39 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920131</v>
+        <v>22330051920247</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920132</v>
+        <v>22330051920247</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
         <v>64</v>
@@ -4840,39 +4840,39 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920132</v>
+        <v>22330051920348</v>
       </c>
       <c r="B12" t="s">
         <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920135</v>
+        <v>22330051920136</v>
       </c>
       <c r="B13" t="s">
         <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
         <v>64</v>
@@ -4880,59 +4880,59 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920244</v>
+        <v>22330051920351</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920244</v>
+        <v>22330051920351</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920346</v>
+        <v>22330051920139</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
         <v>64</v>
@@ -4940,19 +4940,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920346</v>
+        <v>22330051920352</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
         <v>65</v>
@@ -4960,19 +4960,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920129</v>
+        <v>22330051920352</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
         <v>64</v>
@@ -4980,19 +4980,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>22330051920247</v>
+        <v>22330051920141</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
         <v>64</v>
@@ -5000,542 +5000,102 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>22330051920247</v>
+        <v>22330051920142</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>22330051920348</v>
+        <v>22330051920354</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>22330051920136</v>
+        <v>22330051920144</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>22330051920136</v>
+        <v>22330051920144</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>22330051920350</v>
+        <v>22330051920258</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920138</v>
-      </c>
-      <c r="B25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" t="s">
-        <v>112</v>
-      </c>
-      <c r="D25" t="s">
-        <v>138</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920351</v>
-      </c>
-      <c r="B26" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" t="s">
-        <v>113</v>
-      </c>
-      <c r="D26" t="s">
-        <v>139</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920351</v>
-      </c>
-      <c r="B27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" t="s">
-        <v>113</v>
-      </c>
-      <c r="D27" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920139</v>
-      </c>
-      <c r="B28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C28" t="s">
-        <v>114</v>
-      </c>
-      <c r="D28" t="s">
-        <v>140</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920139</v>
-      </c>
-      <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" t="s">
-        <v>114</v>
-      </c>
-      <c r="D29" t="s">
-        <v>140</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>22330051920110</v>
-      </c>
-      <c r="B30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30" t="s">
-        <v>141</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>22330051920140</v>
-      </c>
-      <c r="B31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" t="s">
-        <v>115</v>
-      </c>
-      <c r="D31" t="s">
-        <v>142</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>22330051920352</v>
-      </c>
-      <c r="B32" t="s">
-        <v>94</v>
-      </c>
-      <c r="C32" t="s">
-        <v>116</v>
-      </c>
-      <c r="D32" t="s">
-        <v>143</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>22330051920352</v>
-      </c>
-      <c r="B33" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" t="s">
-        <v>116</v>
-      </c>
-      <c r="D33" t="s">
-        <v>143</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>22330051920141</v>
-      </c>
-      <c r="B34" t="s">
-        <v>95</v>
-      </c>
-      <c r="C34" t="s">
-        <v>117</v>
-      </c>
-      <c r="D34" t="s">
-        <v>144</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>22330051920141</v>
-      </c>
-      <c r="B35" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" t="s">
-        <v>117</v>
-      </c>
-      <c r="D35" t="s">
-        <v>144</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>22330051920142</v>
-      </c>
-      <c r="B36" t="s">
-        <v>96</v>
-      </c>
-      <c r="C36" t="s">
-        <v>95</v>
-      </c>
-      <c r="D36" t="s">
-        <v>145</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>22330051920142</v>
-      </c>
-      <c r="B37" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37" t="s">
-        <v>145</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>22330051920354</v>
-      </c>
-      <c r="B38" t="s">
-        <v>97</v>
-      </c>
-      <c r="C38" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" t="s">
-        <v>146</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>22330051920354</v>
-      </c>
-      <c r="B39" t="s">
-        <v>97</v>
-      </c>
-      <c r="C39" t="s">
-        <v>118</v>
-      </c>
-      <c r="D39" t="s">
-        <v>146</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>22330051920143</v>
-      </c>
-      <c r="B40" t="s">
-        <v>98</v>
-      </c>
-      <c r="C40" t="s">
-        <v>116</v>
-      </c>
-      <c r="D40" t="s">
-        <v>147</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>22330051920144</v>
-      </c>
-      <c r="B41" t="s">
-        <v>99</v>
-      </c>
-      <c r="C41" t="s">
-        <v>119</v>
-      </c>
-      <c r="D41" t="s">
-        <v>148</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>22330051920144</v>
-      </c>
-      <c r="B42" t="s">
-        <v>99</v>
-      </c>
-      <c r="C42" t="s">
-        <v>119</v>
-      </c>
-      <c r="D42" t="s">
-        <v>148</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>22330051920145</v>
-      </c>
-      <c r="B43" t="s">
-        <v>99</v>
-      </c>
-      <c r="C43" t="s">
-        <v>120</v>
-      </c>
-      <c r="D43" t="s">
-        <v>149</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>22330051920146</v>
-      </c>
-      <c r="B44" t="s">
-        <v>100</v>
-      </c>
-      <c r="C44" t="s">
-        <v>79</v>
-      </c>
-      <c r="D44" t="s">
-        <v>150</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>22330051920258</v>
-      </c>
-      <c r="B45" t="s">
-        <v>101</v>
-      </c>
-      <c r="C45" t="s">
-        <v>121</v>
-      </c>
-      <c r="D45" t="s">
-        <v>151</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>22330051920258</v>
-      </c>
-      <c r="B46" t="s">
-        <v>101</v>
-      </c>
-      <c r="C46" t="s">
-        <v>121</v>
-      </c>
-      <c r="D46" t="s">
-        <v>151</v>
-      </c>
-      <c r="E46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -5571,16 +5131,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920124</v>
+        <v>22330051920244</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -5588,16 +5148,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920126</v>
+        <v>22330051920346</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -5605,16 +5165,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920132</v>
+        <v>22330051920247</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -5622,16 +5182,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920244</v>
+        <v>22330051920351</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -5639,16 +5199,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920346</v>
+        <v>22330051920352</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -5656,16 +5216,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920247</v>
+        <v>22330051920144</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -5673,169 +5233,169 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920136</v>
+        <v>22330051920124</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920351</v>
+        <v>22330051920342</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920139</v>
+        <v>22330051920126</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920352</v>
+        <v>22330051920132</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920141</v>
+        <v>22330051920348</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920142</v>
+        <v>22330051920136</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920354</v>
+        <v>22330051920139</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920144</v>
+        <v>22330051920141</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920258</v>
+        <v>22330051920142</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920343</v>
+        <v>22330051920354</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -5843,16 +5403,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920342</v>
+        <v>22330051920258</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -5860,234 +5420,234 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920344</v>
+        <v>22330051920343</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920130</v>
+        <v>22330051920125</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920131</v>
+        <v>22330051920344</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="D21" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920135</v>
+        <v>22330051920127</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920129</v>
+        <v>22330051920345</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D23" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920348</v>
+        <v>22330051920128</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920350</v>
+        <v>22330051920130</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="D25" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920138</v>
+        <v>22330051920131</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="C26" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="D26" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920110</v>
+        <v>22330051920133</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920140</v>
+        <v>22330051920134</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920143</v>
+        <v>22330051920135</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920145</v>
+        <v>22330051920129</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="D30" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920146</v>
+        <v>22330051920347</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="D31" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920125</v>
+        <v>22330051920349</v>
       </c>
       <c r="B32" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="C32" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="D32" t="s">
         <v>171</v>
@@ -6098,13 +5658,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330051920127</v>
+        <v>22330051920137</v>
       </c>
       <c r="B33" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="C33" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D33" t="s">
         <v>172</v>
@@ -6115,13 +5675,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920345</v>
+        <v>22330051920350</v>
       </c>
       <c r="B34" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="C34" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="D34" t="s">
         <v>173</v>
@@ -6132,13 +5692,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>22330051920128</v>
+        <v>22330051920138</v>
       </c>
       <c r="B35" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="C35" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="D35" t="s">
         <v>174</v>
@@ -6149,13 +5709,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>22330051920133</v>
+        <v>22330051920110</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D36" t="s">
         <v>175</v>
@@ -6166,13 +5726,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>22330051920134</v>
+        <v>22330051920140</v>
       </c>
       <c r="B37" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="C37" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="D37" t="s">
         <v>176</v>
@@ -6183,13 +5743,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>22330051920347</v>
+        <v>22330051920353</v>
       </c>
       <c r="B38" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="C38" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="D38" t="s">
         <v>177</v>
@@ -6200,13 +5760,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>22330051920349</v>
+        <v>22330051920143</v>
       </c>
       <c r="B39" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="C39" t="s">
-        <v>166</v>
+        <v>100</v>
       </c>
       <c r="D39" t="s">
         <v>178</v>
@@ -6217,13 +5777,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>22330051920137</v>
+        <v>22330051920145</v>
       </c>
       <c r="B40" t="s">
-        <v>158</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="D40" t="s">
         <v>179</v>
@@ -6234,13 +5794,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>22330051920353</v>
+        <v>22330051920146</v>
       </c>
       <c r="B41" t="s">
-        <v>159</v>
+        <v>92</v>
       </c>
       <c r="C41" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="D41" t="s">
         <v>180</v>
@@ -6254,10 +5814,10 @@
         <v>22330051920355</v>
       </c>
       <c r="B42" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D42" t="s">
         <v>181</v>
@@ -6271,10 +5831,10 @@
         <v>22330051920147</v>
       </c>
       <c r="B43" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C43" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="D43" t="s">
         <v>182</v>
@@ -6288,10 +5848,10 @@
         <v>22330051920148</v>
       </c>
       <c r="B44" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="C44" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="D44" t="s">
         <v>183</v>
@@ -6307,7 +5867,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6339,68 +5899,68 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920124</v>
+        <v>22330051920131</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920124</v>
+        <v>22330051920131</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920126</v>
+        <v>22330051920346</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -6408,22 +5968,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920126</v>
+        <v>22330051920346</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -6431,22 +5991,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920130</v>
+        <v>22330051920247</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -6454,88 +6014,88 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920130</v>
+        <v>22330051920247</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920131</v>
+        <v>22330051920348</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920131</v>
+        <v>22330051920348</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920132</v>
+        <v>22330051920136</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>64</v>
@@ -6546,42 +6106,42 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920132</v>
+        <v>22330051920136</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920346</v>
+        <v>22330051920141</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
         <v>64</v>
@@ -6592,68 +6152,68 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920346</v>
+        <v>22330051920141</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920247</v>
+        <v>22330051920354</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920247</v>
+        <v>22330051920354</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -6661,45 +6221,45 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920348</v>
+        <v>22330051920124</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920348</v>
+        <v>22330051920342</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
         <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G17">
         <v>-1</v>
@@ -6707,45 +6267,45 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920354</v>
+        <v>22330051920125</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920354</v>
+        <v>22330051920126</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G19">
         <v>-1</v>
@@ -6753,45 +6313,45 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920258</v>
+        <v>22330051920130</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="D20" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920258</v>
+        <v>22330051920132</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
-        <v>151</v>
+        <v>108</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G21">
         <v>-1</v>
@@ -6799,300 +6359,24 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920343</v>
+        <v>22330051920258</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
         <v>64</v>
       </c>
       <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920342</v>
-      </c>
-      <c r="B23" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" t="s">
-        <v>100</v>
-      </c>
-      <c r="D23" t="s">
-        <v>124</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920125</v>
-      </c>
-      <c r="B24" t="s">
-        <v>152</v>
-      </c>
-      <c r="C24" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" t="s">
-        <v>171</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920344</v>
-      </c>
-      <c r="B25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" t="s">
-        <v>126</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920135</v>
-      </c>
-      <c r="B26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" t="s">
-        <v>86</v>
-      </c>
-      <c r="D26" t="s">
-        <v>130</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920129</v>
-      </c>
-      <c r="B27" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" t="s">
-        <v>133</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>64</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>22330051920350</v>
-      </c>
-      <c r="B28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" t="s">
-        <v>137</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>64</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>22330051920138</v>
-      </c>
-      <c r="B29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" t="s">
-        <v>138</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>64</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>22330051920110</v>
-      </c>
-      <c r="B30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30" t="s">
-        <v>141</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>64</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>22330051920140</v>
-      </c>
-      <c r="B31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" t="s">
-        <v>115</v>
-      </c>
-      <c r="D31" t="s">
-        <v>142</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>64</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>22330051920143</v>
-      </c>
-      <c r="B32" t="s">
-        <v>98</v>
-      </c>
-      <c r="C32" t="s">
-        <v>116</v>
-      </c>
-      <c r="D32" t="s">
-        <v>147</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>64</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>22330051920145</v>
-      </c>
-      <c r="B33" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" t="s">
-        <v>120</v>
-      </c>
-      <c r="D33" t="s">
-        <v>149</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>64</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>22330051920146</v>
-      </c>
-      <c r="B34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34" t="s">
-        <v>79</v>
-      </c>
-      <c r="D34" t="s">
-        <v>150</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>64</v>
-      </c>
-      <c r="G34">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/1EM - Estadisticos 20221.xlsx
+++ b/grupos/1EM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="184">
   <si>
     <t>Materia</t>
   </si>
@@ -215,21 +215,21 @@
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -245,36 +245,90 @@
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>ARZATE</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
+    <t>APONTE</t>
+  </si>
+  <si>
     <t>CARRILLO</t>
   </si>
   <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>LUNA</t>
   </si>
   <si>
+    <t>MARCIAL</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
     <t>MAY</t>
   </si>
   <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MENCIAS</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
     <t>NEPOMUCENO</t>
   </si>
   <si>
     <t>ORTEGA</t>
   </si>
   <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
     <t>PIÑA</t>
   </si>
   <si>
@@ -284,43 +338,85 @@
     <t>ROSAS</t>
   </si>
   <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
     <t>SOLANO</t>
   </si>
   <si>
+    <t>TENORIO</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>VEGA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
+    <t>VIÑAS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>BAEZ</t>
   </si>
   <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>ZEPACTLE</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>PELLICO</t>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>ACAHUA</t>
   </si>
   <si>
     <t>SERRANO</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>MONTIEL</t>
   </si>
   <si>
     <t>VIDERIQUE</t>
@@ -332,42 +428,111 @@
     <t>MEZA</t>
   </si>
   <si>
+    <t>SALAS</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>TOBIAS</t>
   </si>
   <si>
+    <t>LUCIANA</t>
+  </si>
+  <si>
     <t>LEONOR</t>
   </si>
   <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
     <t>ESTEFANY CELESTE</t>
   </si>
   <si>
+    <t>DARA NAOMI</t>
+  </si>
+  <si>
+    <t>MAYRA</t>
+  </si>
+  <si>
+    <t>JULIANA</t>
+  </si>
+  <si>
+    <t>KARENT LILIANA</t>
+  </si>
+  <si>
+    <t>ABIGAIL ANTONIA</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
     <t>XIMENA</t>
   </si>
   <si>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>MARIA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>DANNA ANGELA</t>
+  </si>
+  <si>
     <t>ALEXIS</t>
   </si>
   <si>
     <t>GUSTAVO KALEL</t>
   </si>
   <si>
+    <t>ILSE MARIA</t>
+  </si>
+  <si>
     <t>KAREN</t>
   </si>
   <si>
+    <t>ALANIS YUMEI</t>
+  </si>
+  <si>
     <t>FLORENTINA ESMERALDA</t>
   </si>
   <si>
     <t>GABRIELA AIMEE</t>
   </si>
   <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>FELIX RAFAEL</t>
+  </si>
+  <si>
+    <t>JOSELYN</t>
+  </si>
+  <si>
+    <t>ZURI GABRIELA</t>
+  </si>
+  <si>
     <t>DYLAN NAHIM</t>
   </si>
   <si>
     <t>ERICK</t>
   </si>
   <si>
+    <t>ODALIS SOFIA</t>
+  </si>
+  <si>
+    <t>JESUS ADRIAN</t>
+  </si>
+  <si>
     <t>DULCE MARIA</t>
   </si>
   <si>
@@ -377,190 +542,25 @@
     <t>ESTEFANY VIANEY</t>
   </si>
   <si>
+    <t>AZUL ARIADNA</t>
+  </si>
+  <si>
     <t>KEVIN</t>
   </si>
   <si>
+    <t>ORESTES</t>
+  </si>
+  <si>
     <t>ACSA FERNANDA</t>
   </si>
   <si>
+    <t>MELISA VIANNEY</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
     <t>NERY JOSELYN</t>
-  </si>
-  <si>
-    <t>ARZATE</t>
-  </si>
-  <si>
-    <t>APONTE</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MARCIAL</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MENCIAS</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>TENORIO</t>
-  </si>
-  <si>
-    <t>VIÑAS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>ZEPACTLE</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>ACAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>LUCIANA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>DARA NAOMI</t>
-  </si>
-  <si>
-    <t>MAYRA</t>
-  </si>
-  <si>
-    <t>JULIANA</t>
-  </si>
-  <si>
-    <t>KARENT LILIANA</t>
-  </si>
-  <si>
-    <t>ABIGAIL ANTONIA</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
-    <t>MARIA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>DANNA ANGELA</t>
-  </si>
-  <si>
-    <t>ILSE MARIA</t>
-  </si>
-  <si>
-    <t>ALANIS YUMEI</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>FELIX RAFAEL</t>
-  </si>
-  <si>
-    <t>JOSELYN</t>
-  </si>
-  <si>
-    <t>ZURI GABRIELA</t>
-  </si>
-  <si>
-    <t>ODALIS SOFIA</t>
-  </si>
-  <si>
-    <t>JESUS ADRIAN</t>
-  </si>
-  <si>
-    <t>AZUL ARIADNA</t>
-  </si>
-  <si>
-    <t>ORESTES</t>
-  </si>
-  <si>
-    <t>MELISA VIANNEY</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
   </si>
   <si>
     <t>REYNA LINDA</t>
@@ -1067,16 +1067,16 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>-1</v>
@@ -1085,7 +1085,7 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1112,7 +1112,7 @@
         <v>6</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -1121,7 +1121,7 @@
         <v>6</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -1150,10 +1150,10 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -1162,7 +1162,7 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1186,7 +1186,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>10</v>
@@ -1221,16 +1221,16 @@
         <v>7</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -1239,7 +1239,7 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1263,10 +1263,10 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>8</v>
@@ -1275,7 +1275,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1304,10 +1304,10 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1316,7 +1316,7 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1340,7 +1340,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>10</v>
@@ -1352,7 +1352,7 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1381,10 +1381,10 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1393,7 +1393,7 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1417,10 +1417,10 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -1452,16 +1452,16 @@
         <v>6</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G9">
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1470,7 +1470,7 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1506,7 +1506,7 @@
         <v>6</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1535,10 +1535,10 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1547,7 +1547,7 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1583,7 +1583,7 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -1612,10 +1612,10 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -1624,7 +1624,7 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1689,10 +1689,10 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1701,7 +1701,7 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1766,10 +1766,10 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1778,7 +1778,7 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1802,7 +1802,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1843,10 +1843,10 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -1855,7 +1855,7 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1891,7 +1891,7 @@
         <v>6</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1920,10 +1920,10 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -1932,7 +1932,7 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1956,7 +1956,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1968,7 +1968,7 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1991,16 +1991,16 @@
         <v>6</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G16">
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -2009,7 +2009,7 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -2045,7 +2045,7 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -2074,10 +2074,10 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -2086,7 +2086,7 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2151,10 +2151,10 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>-1</v>
@@ -2163,7 +2163,7 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2228,10 +2228,10 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2240,7 +2240,7 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2264,7 +2264,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>10</v>
@@ -2276,7 +2276,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2293,22 +2293,22 @@
         <v>9</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E20">
         <v>5</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G20">
         <v>7</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -2317,7 +2317,7 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2344,16 +2344,16 @@
         <v>7</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>5</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2370,22 +2370,22 @@
         <v>9</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>6</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G21">
         <v>8</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -2394,7 +2394,7 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2421,16 +2421,16 @@
         <v>6</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>6</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2447,22 +2447,22 @@
         <v>10</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>6</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G22">
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2471,7 +2471,7 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2498,16 +2498,16 @@
         <v>7</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>6</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -2536,10 +2536,10 @@
         <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2548,7 +2548,7 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2607,16 +2607,16 @@
         <v>5</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G24">
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>-1</v>
@@ -2625,7 +2625,7 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2649,7 +2649,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -2661,7 +2661,7 @@
         <v>5</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>9</v>
@@ -2684,16 +2684,16 @@
         <v>7</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G25">
         <v>5</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -2702,7 +2702,7 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2729,7 +2729,7 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>6</v>
@@ -2738,7 +2738,7 @@
         <v>7</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y25">
         <v>5</v>
@@ -2767,10 +2767,10 @@
         <v>9</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -2779,7 +2779,7 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2803,7 +2803,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>10</v>
@@ -2844,10 +2844,10 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -2856,7 +2856,7 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2880,7 +2880,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>10</v>
@@ -2921,10 +2921,10 @@
         <v>9</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -2933,7 +2933,7 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2957,7 +2957,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -2969,7 +2969,7 @@
         <v>9</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -2998,10 +2998,10 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
         <v>-1</v>
@@ -3010,7 +3010,7 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -3034,10 +3034,10 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>6</v>
@@ -3046,7 +3046,7 @@
         <v>6</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -3063,22 +3063,22 @@
         <v>5</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E30">
         <v>5</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G30">
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
         <v>-1</v>
@@ -3087,7 +3087,7 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3114,16 +3114,16 @@
         <v>6</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>5</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y30">
         <v>5</v>
@@ -3146,16 +3146,16 @@
         <v>6</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G31">
         <v>5</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
         <v>-1</v>
@@ -3164,7 +3164,7 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3188,10 +3188,10 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>5</v>
@@ -3200,7 +3200,7 @@
         <v>6</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -3229,10 +3229,10 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
         <v>-1</v>
@@ -3241,7 +3241,7 @@
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3265,7 +3265,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>10</v>
@@ -3277,7 +3277,7 @@
         <v>6</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>6</v>
@@ -3294,22 +3294,22 @@
         <v>8</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E33">
         <v>5</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G33">
         <v>5</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>-1</v>
@@ -3318,7 +3318,7 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3342,19 +3342,19 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W33">
         <v>5</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y33">
         <v>5</v>
@@ -3383,10 +3383,10 @@
         <v>8</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -3395,7 +3395,7 @@
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3419,7 +3419,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U34">
         <v>10</v>
@@ -3454,16 +3454,16 @@
         <v>6</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G35">
         <v>5</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
         <v>-1</v>
@@ -3472,7 +3472,7 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3499,7 +3499,7 @@
         <v>6</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -3508,7 +3508,7 @@
         <v>6</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y35">
         <v>5</v>
@@ -3531,16 +3531,16 @@
         <v>5</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G36">
         <v>5</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
         <v>-1</v>
@@ -3549,7 +3549,7 @@
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3573,10 +3573,10 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V36">
         <v>6</v>
@@ -3585,7 +3585,7 @@
         <v>5</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>5</v>
@@ -3614,10 +3614,10 @@
         <v>10</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J37">
         <v>-1</v>
@@ -3626,7 +3626,7 @@
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3685,16 +3685,16 @@
         <v>7</v>
       </c>
       <c r="F38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G38">
         <v>7</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J38">
         <v>-1</v>
@@ -3703,7 +3703,7 @@
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M38">
         <v>-1</v>
@@ -3739,7 +3739,7 @@
         <v>7</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y38">
         <v>7</v>
@@ -3768,10 +3768,10 @@
         <v>8</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J39">
         <v>-1</v>
@@ -3780,7 +3780,7 @@
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M39">
         <v>-1</v>
@@ -3804,10 +3804,10 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V39">
         <v>7</v>
@@ -3833,22 +3833,22 @@
         <v>9</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E40">
         <v>5</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G40">
         <v>6</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J40">
         <v>-1</v>
@@ -3857,7 +3857,7 @@
         <v>-1</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M40">
         <v>-1</v>
@@ -3881,19 +3881,19 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W40">
         <v>5</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y40">
         <v>6</v>
@@ -3922,10 +3922,10 @@
         <v>8</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J41">
         <v>-1</v>
@@ -3934,7 +3934,7 @@
         <v>-1</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M41">
         <v>-1</v>
@@ -3958,10 +3958,10 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V41">
         <v>7</v>
@@ -3993,16 +3993,16 @@
         <v>6</v>
       </c>
       <c r="F42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G42">
         <v>6</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J42">
         <v>-1</v>
@@ -4011,7 +4011,7 @@
         <v>-1</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M42">
         <v>-1</v>
@@ -4038,7 +4038,7 @@
         <v>6</v>
       </c>
       <c r="U42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V42">
         <v>6</v>
@@ -4047,7 +4047,7 @@
         <v>6</v>
       </c>
       <c r="X42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y42">
         <v>6</v>
@@ -4076,10 +4076,10 @@
         <v>7</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J43">
         <v>-1</v>
@@ -4088,7 +4088,7 @@
         <v>-1</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M43">
         <v>-1</v>
@@ -4112,7 +4112,7 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U43">
         <v>10</v>
@@ -4153,10 +4153,10 @@
         <v>6</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J44">
         <v>-1</v>
@@ -4165,7 +4165,7 @@
         <v>-1</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M44">
         <v>-1</v>
@@ -4230,10 +4230,10 @@
         <v>10</v>
       </c>
       <c r="H45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J45">
         <v>-1</v>
@@ -4242,7 +4242,7 @@
         <v>-1</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M45">
         <v>-1</v>
@@ -4307,10 +4307,10 @@
         <v>7</v>
       </c>
       <c r="H46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J46">
         <v>-1</v>
@@ -4319,7 +4319,7 @@
         <v>-1</v>
       </c>
       <c r="L46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M46">
         <v>-1</v>
@@ -4343,10 +4343,10 @@
         <v>-1</v>
       </c>
       <c r="T46">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U46">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V46">
         <v>8</v>
@@ -4423,30 +4423,30 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>60.47</v>
+        <v>67.44</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>32.56</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>39.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -4458,27 +4458,27 @@
         <v>34</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>79.06999999999999</v>
       </c>
       <c r="G3">
-        <v>6.98</v>
+        <v>20.93</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>13.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -4487,16 +4487,16 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>79.06999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G4">
-        <v>20.93</v>
+        <v>18.6</v>
       </c>
       <c r="H4">
         <v>7.1</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
@@ -4563,7 +4563,7 @@
         <v>4.65</v>
       </c>
       <c r="H6">
-        <v>9.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>69</v>
@@ -4595,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4611,7 +4611,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4636,466 +4636,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920124</v>
-      </c>
-      <c r="B2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920342</v>
-      </c>
-      <c r="B3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920126</v>
-      </c>
-      <c r="B4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920132</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920244</v>
-      </c>
-      <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920244</v>
-      </c>
-      <c r="B7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920346</v>
-      </c>
-      <c r="B8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" t="s">
-        <v>110</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920346</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" t="s">
-        <v>110</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920247</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" t="s">
-        <v>111</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920247</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" t="s">
-        <v>111</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920348</v>
-      </c>
-      <c r="B12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" t="s">
-        <v>112</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920136</v>
-      </c>
-      <c r="B13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" t="s">
-        <v>113</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920351</v>
-      </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920351</v>
-      </c>
-      <c r="B15" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920139</v>
-      </c>
-      <c r="B16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" t="s">
-        <v>99</v>
-      </c>
-      <c r="D16" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920352</v>
-      </c>
-      <c r="B17" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" t="s">
-        <v>100</v>
-      </c>
-      <c r="D17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920352</v>
-      </c>
-      <c r="B18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" t="s">
-        <v>100</v>
-      </c>
-      <c r="D18" t="s">
-        <v>116</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920141</v>
-      </c>
-      <c r="B19" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" t="s">
-        <v>117</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920142</v>
-      </c>
-      <c r="B20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" t="s">
-        <v>118</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920354</v>
-      </c>
-      <c r="B21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21" t="s">
-        <v>119</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920144</v>
-      </c>
-      <c r="B22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" t="s">
-        <v>120</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920144</v>
-      </c>
-      <c r="B23" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" t="s">
-        <v>103</v>
-      </c>
-      <c r="D23" t="s">
-        <v>120</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920258</v>
-      </c>
-      <c r="B24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" t="s">
-        <v>121</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -5131,302 +4671,302 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920244</v>
+        <v>22330051920124</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920346</v>
+        <v>22330051920343</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920247</v>
+        <v>22330051920342</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920351</v>
+        <v>22330051920125</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920352</v>
+        <v>22330051920126</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920144</v>
+        <v>22330051920344</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920124</v>
+        <v>22330051920127</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920342</v>
+        <v>22330051920345</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>148</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920126</v>
+        <v>22330051920128</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>149</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920132</v>
+        <v>22330051920130</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920348</v>
+        <v>22330051920131</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920136</v>
+        <v>22330051920132</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920139</v>
+        <v>22330051920133</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920141</v>
+        <v>22330051920134</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920142</v>
+        <v>22330051920135</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920354</v>
+        <v>22330051920244</v>
       </c>
       <c r="B17" t="s">
         <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920258</v>
+        <v>22330051920346</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920343</v>
+        <v>22330051920129</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="D19" t="s">
         <v>158</v>
@@ -5437,13 +4977,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920125</v>
+        <v>22330051920247</v>
       </c>
       <c r="B20" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="D20" t="s">
         <v>159</v>
@@ -5454,13 +4994,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920344</v>
+        <v>22330051920347</v>
       </c>
       <c r="B21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s">
         <v>124</v>
-      </c>
-      <c r="C21" t="s">
-        <v>130</v>
       </c>
       <c r="D21" t="s">
         <v>160</v>
@@ -5471,13 +5011,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920127</v>
+        <v>22330051920348</v>
       </c>
       <c r="B22" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
         <v>161</v>
@@ -5488,13 +5028,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920345</v>
+        <v>22330051920136</v>
       </c>
       <c r="B23" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
         <v>162</v>
@@ -5505,13 +5045,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920128</v>
+        <v>22330051920349</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
         <v>163</v>
@@ -5522,13 +5062,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920130</v>
+        <v>22330051920137</v>
       </c>
       <c r="B25" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
         <v>164</v>
@@ -5539,13 +5079,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920131</v>
+        <v>22330051920350</v>
       </c>
       <c r="B26" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="D26" t="s">
         <v>165</v>
@@ -5556,13 +5096,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920133</v>
+        <v>22330051920138</v>
       </c>
       <c r="B27" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
         <v>166</v>
@@ -5573,13 +5113,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920134</v>
+        <v>22330051920351</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
         <v>167</v>
@@ -5590,13 +5130,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920135</v>
+        <v>22330051920139</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="D29" t="s">
         <v>168</v>
@@ -5607,13 +5147,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920129</v>
+        <v>22330051920110</v>
       </c>
       <c r="B30" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
         <v>169</v>
@@ -5624,13 +5164,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920347</v>
+        <v>22330051920140</v>
       </c>
       <c r="B31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" t="s">
         <v>132</v>
-      </c>
-      <c r="C31" t="s">
-        <v>148</v>
       </c>
       <c r="D31" t="s">
         <v>170</v>
@@ -5641,13 +5181,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920349</v>
+        <v>22330051920352</v>
       </c>
       <c r="B32" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s">
         <v>171</v>
@@ -5658,13 +5198,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330051920137</v>
+        <v>22330051920141</v>
       </c>
       <c r="B33" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="C33" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s">
         <v>172</v>
@@ -5675,13 +5215,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920350</v>
+        <v>22330051920142</v>
       </c>
       <c r="B34" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="D34" t="s">
         <v>173</v>
@@ -5692,13 +5232,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>22330051920138</v>
+        <v>22330051920353</v>
       </c>
       <c r="B35" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="C35" t="s">
-        <v>152</v>
+        <v>113</v>
       </c>
       <c r="D35" t="s">
         <v>174</v>
@@ -5709,13 +5249,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>22330051920110</v>
+        <v>22330051920354</v>
       </c>
       <c r="B36" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="D36" t="s">
         <v>175</v>
@@ -5726,13 +5266,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>22330051920140</v>
+        <v>22330051920143</v>
       </c>
       <c r="B37" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="C37" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="D37" t="s">
         <v>176</v>
@@ -5743,13 +5283,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>22330051920353</v>
+        <v>22330051920144</v>
       </c>
       <c r="B38" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D38" t="s">
         <v>177</v>
@@ -5760,13 +5300,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>22330051920143</v>
+        <v>22330051920145</v>
       </c>
       <c r="B39" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="D39" t="s">
         <v>178</v>
@@ -5777,13 +5317,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>22330051920145</v>
+        <v>22330051920146</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="C40" t="s">
-        <v>154</v>
+        <v>83</v>
       </c>
       <c r="D40" t="s">
         <v>179</v>
@@ -5794,13 +5334,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>22330051920146</v>
+        <v>22330051920258</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="C41" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D41" t="s">
         <v>180</v>
@@ -5814,10 +5354,10 @@
         <v>22330051920355</v>
       </c>
       <c r="B42" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="C42" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="D42" t="s">
         <v>181</v>
@@ -5831,10 +5371,10 @@
         <v>22330051920147</v>
       </c>
       <c r="B43" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="C43" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="D43" t="s">
         <v>182</v>
@@ -5848,10 +5388,10 @@
         <v>22330051920148</v>
       </c>
       <c r="B44" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="C44" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="D44" t="s">
         <v>183</v>
@@ -5867,7 +5407,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5902,19 +5442,19 @@
         <v>22330051920131</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="D2" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5925,19 +5465,19 @@
         <v>22330051920131</v>
       </c>
       <c r="B3" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5945,39 +5485,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920346</v>
+        <v>22330051920247</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920346</v>
+        <v>22330051920247</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5986,73 +5526,73 @@
         <v>64</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920247</v>
+        <v>22330051920136</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920247</v>
+        <v>22330051920136</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920348</v>
+        <v>22330051920141</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6060,68 +5600,68 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920348</v>
+        <v>22330051920141</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920136</v>
+        <v>22330051920142</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920136</v>
+        <v>22330051920142</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6129,16 +5669,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920141</v>
+        <v>22330051920343</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -6147,27 +5687,27 @@
         <v>64</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920141</v>
+        <v>22330051920342</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -6175,19 +5715,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920354</v>
+        <v>22330051920125</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>65</v>
@@ -6198,16 +5738,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920354</v>
+        <v>22330051920126</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -6216,44 +5756,44 @@
         <v>64</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920124</v>
+        <v>22330051920130</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920342</v>
+        <v>22330051920346</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>157</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -6262,27 +5802,27 @@
         <v>64</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920125</v>
+        <v>22330051920348</v>
       </c>
       <c r="B18" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -6290,16 +5830,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920126</v>
+        <v>22330051920138</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>166</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -6308,24 +5848,24 @@
         <v>64</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920130</v>
+        <v>22330051920354</v>
       </c>
       <c r="B20" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D20" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
@@ -6336,16 +5876,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920132</v>
+        <v>22330051920258</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -6354,30 +5894,7 @@
         <v>64</v>
       </c>
       <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920258</v>
-      </c>
-      <c r="B22" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" t="s">
-        <v>121</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>64</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1EM - Estadisticos 20221.xlsx
+++ b/grupos/1EM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="184">
   <si>
     <t>Materia</t>
   </si>
@@ -215,10 +215,10 @@
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
     <t>García Sánchez Magda Bexabe</t>
@@ -1079,16 +1079,16 @@
         <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1118,13 +1118,13 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1156,16 +1156,16 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1195,7 +1195,7 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -1233,16 +1233,16 @@
         <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1269,7 +1269,7 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1278,7 +1278,7 @@
         <v>5</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1310,16 +1310,16 @@
         <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1349,13 +1349,13 @@
         <v>7</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1387,16 +1387,16 @@
         <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1432,7 +1432,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1464,16 +1464,16 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1509,7 +1509,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1541,16 +1541,16 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1577,10 +1577,10 @@
         <v>10</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>8</v>
@@ -1618,16 +1618,16 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
         <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1695,16 +1695,16 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1731,10 +1731,10 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -1772,16 +1772,16 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
         <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1808,16 +1808,16 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1849,16 +1849,16 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
         <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1885,16 +1885,16 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1926,16 +1926,16 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1965,13 +1965,13 @@
         <v>5</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2003,16 +2003,16 @@
         <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2039,7 +2039,7 @@
         <v>8</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -2048,7 +2048,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2080,16 +2080,16 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2119,13 +2119,13 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X17">
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2157,16 +2157,16 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2234,16 +2234,16 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2270,10 +2270,10 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2311,16 +2311,16 @@
         <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2350,13 +2350,13 @@
         <v>5</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2388,16 +2388,16 @@
         <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2424,10 +2424,10 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>5</v>
@@ -2465,16 +2465,16 @@
         <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2542,16 +2542,16 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
         <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2581,13 +2581,13 @@
         <v>9</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2619,16 +2619,16 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2655,7 +2655,7 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>5</v>
@@ -2664,7 +2664,7 @@
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2696,16 +2696,16 @@
         <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2732,10 +2732,10 @@
         <v>9</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>5</v>
@@ -2773,16 +2773,16 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
         <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2850,16 +2850,16 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2886,10 +2886,10 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>8</v>
@@ -2927,16 +2927,16 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2966,7 +2966,7 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -3004,16 +3004,16 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>5</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3040,10 +3040,10 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>5</v>
@@ -3081,16 +3081,16 @@
         <v>7</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
         <v>5</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3158,16 +3158,16 @@
         <v>5</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
         <v>5</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3197,7 +3197,7 @@
         <v>5</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X31">
         <v>5</v>
@@ -3235,16 +3235,16 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3271,16 +3271,16 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3312,16 +3312,16 @@
         <v>5</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L33">
         <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3389,16 +3389,16 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
         <v>6</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3425,16 +3425,16 @@
         <v>10</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3466,16 +3466,16 @@
         <v>5</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L35">
         <v>5</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3502,10 +3502,10 @@
         <v>7</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X35">
         <v>5</v>
@@ -3543,16 +3543,16 @@
         <v>9</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
         <v>6</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3579,16 +3579,16 @@
         <v>7</v>
       </c>
       <c r="V36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X36">
         <v>6</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3620,16 +3620,16 @@
         <v>9</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
         <v>6</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3659,13 +3659,13 @@
         <v>9</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X37">
         <v>7</v>
       </c>
       <c r="Y37">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3697,16 +3697,16 @@
         <v>7</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
         <v>6</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3736,13 +3736,13 @@
         <v>5</v>
       </c>
       <c r="W38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>6</v>
       </c>
       <c r="Y38">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3774,16 +3774,16 @@
         <v>8</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L39">
         <v>6</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3810,16 +3810,16 @@
         <v>9</v>
       </c>
       <c r="V39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X39">
         <v>6</v>
       </c>
       <c r="Y39">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3851,16 +3851,16 @@
         <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L40">
         <v>6</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3890,13 +3890,13 @@
         <v>5</v>
       </c>
       <c r="W40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X40">
         <v>5</v>
       </c>
       <c r="Y40">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3928,16 +3928,16 @@
         <v>8</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L41">
         <v>6</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3964,7 +3964,7 @@
         <v>9</v>
       </c>
       <c r="V41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W41">
         <v>8</v>
@@ -3973,7 +3973,7 @@
         <v>6</v>
       </c>
       <c r="Y41">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -4005,16 +4005,16 @@
         <v>8</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L42">
         <v>6</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -4041,16 +4041,16 @@
         <v>9</v>
       </c>
       <c r="V42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X42">
         <v>5</v>
       </c>
       <c r="Y42">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -4082,16 +4082,16 @@
         <v>10</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L43">
         <v>7</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -4118,16 +4118,16 @@
         <v>10</v>
       </c>
       <c r="V43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X43">
         <v>7</v>
       </c>
       <c r="Y43">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4159,16 +4159,16 @@
         <v>10</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L44">
         <v>7</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N44">
         <v>-1</v>
@@ -4198,7 +4198,7 @@
         <v>8</v>
       </c>
       <c r="W44">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X44">
         <v>8</v>
@@ -4236,16 +4236,16 @@
         <v>10</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L45">
         <v>9</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N45">
         <v>-1</v>
@@ -4313,16 +4313,16 @@
         <v>10</v>
       </c>
       <c r="J46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L46">
         <v>6</v>
       </c>
       <c r="M46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N46">
         <v>-1</v>
@@ -4352,7 +4352,7 @@
         <v>8</v>
       </c>
       <c r="W46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X46">
         <v>6</v>
@@ -4446,7 +4446,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -4455,19 +4455,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>79.06999999999999</v>
+        <v>74.42</v>
       </c>
       <c r="G3">
-        <v>20.93</v>
+        <v>25.58</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4478,7 +4478,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -4487,19 +4487,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>81.40000000000001</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="G4">
-        <v>18.6</v>
+        <v>23.26</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4531,7 +4531,7 @@
         <v>13.95</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5407,7 +5407,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920131</v>
+        <v>22330051920126</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5462,22 +5462,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920131</v>
+        <v>22330051920126</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5485,22 +5485,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920247</v>
+        <v>22330051920244</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
         <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5508,16 +5508,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920247</v>
+        <v>22330051920244</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
         <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5531,22 +5531,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920136</v>
+        <v>22330051920346</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D6" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5554,22 +5554,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920136</v>
+        <v>22330051920346</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D7" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5577,22 +5577,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920141</v>
+        <v>22330051920247</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5600,22 +5600,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920141</v>
+        <v>22330051920247</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D9" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5623,22 +5623,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920142</v>
+        <v>22330051920144</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="D10" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5646,22 +5646,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920142</v>
+        <v>22330051920144</v>
       </c>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="D11" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920343</v>
+        <v>22330051920124</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5692,16 +5692,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920342</v>
+        <v>22330051920343</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -5715,22 +5715,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920125</v>
+        <v>22330051920342</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5738,22 +5738,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920126</v>
+        <v>22330051920125</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -5761,19 +5761,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920130</v>
+        <v>22330051920131</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
         <v>65</v>
@@ -5784,22 +5784,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920346</v>
+        <v>22330051920132</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -5868,32 +5868,9 @@
         <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920258</v>
-      </c>
-      <c r="B21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C21" t="s">
-        <v>137</v>
-      </c>
-      <c r="D21" t="s">
-        <v>180</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>64</v>
-      </c>
-      <c r="G21">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EM - Estadisticos 20221.xlsx
+++ b/grupos/1EM - Estadisticos 20221.xlsx
@@ -1094,7 +1094,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1112,7 +1112,7 @@
         <v>6</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -1171,7 +1171,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1189,7 +1189,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -1248,7 +1248,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1325,7 +1325,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1343,7 +1343,7 @@
         <v>8</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>7</v>
@@ -1402,7 +1402,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1420,7 +1420,7 @@
         <v>7</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -1479,7 +1479,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1497,7 +1497,7 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>6</v>
@@ -1556,7 +1556,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1633,7 +1633,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1710,7 +1710,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1728,7 +1728,7 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -1787,7 +1787,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1864,7 +1864,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1941,7 +1941,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -2018,7 +2018,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2036,7 +2036,7 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -2095,7 +2095,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2113,7 +2113,7 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -2172,7 +2172,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2249,7 +2249,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2326,7 +2326,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2403,7 +2403,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2421,7 +2421,7 @@
         <v>6</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -2480,7 +2480,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2557,7 +2557,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2634,7 +2634,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2711,7 +2711,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2729,7 +2729,7 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>5</v>
@@ -2788,7 +2788,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2865,7 +2865,7 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2942,7 +2942,7 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3019,7 +3019,7 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3037,7 +3037,7 @@
         <v>8</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -3096,7 +3096,7 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3114,7 +3114,7 @@
         <v>6</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V30">
         <v>5</v>
@@ -3173,7 +3173,7 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3191,7 +3191,7 @@
         <v>5</v>
       </c>
       <c r="U31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V31">
         <v>5</v>
@@ -3250,7 +3250,7 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3327,7 +3327,7 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3345,7 +3345,7 @@
         <v>5</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V33">
         <v>5</v>
@@ -3404,7 +3404,7 @@
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3422,7 +3422,7 @@
         <v>9</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3558,7 +3558,7 @@
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3635,7 +3635,7 @@
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3653,7 +3653,7 @@
         <v>9</v>
       </c>
       <c r="U37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V37">
         <v>9</v>
@@ -3712,7 +3712,7 @@
         <v>-1</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -3730,7 +3730,7 @@
         <v>6</v>
       </c>
       <c r="U38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V38">
         <v>5</v>
@@ -3789,7 +3789,7 @@
         <v>-1</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -3866,7 +3866,7 @@
         <v>-1</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -3943,7 +3943,7 @@
         <v>-1</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P41">
         <v>-1</v>
@@ -4020,7 +4020,7 @@
         <v>-1</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P42">
         <v>-1</v>
@@ -4038,7 +4038,7 @@
         <v>6</v>
       </c>
       <c r="U42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V42">
         <v>5</v>
@@ -4097,7 +4097,7 @@
         <v>-1</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P43">
         <v>-1</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P44">
         <v>-1</v>
@@ -4251,7 +4251,7 @@
         <v>-1</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P45">
         <v>-1</v>
@@ -4328,7 +4328,7 @@
         <v>-1</v>
       </c>
       <c r="O46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P46">
         <v>-1</v>
@@ -4583,19 +4583,19 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="H7">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/1EM - Estadisticos 20221.xlsx
+++ b/grupos/1EM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="184">
   <si>
     <t>Materia</t>
   </si>
@@ -218,16 +218,16 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
+    <t>Moreno Aroyo Anél</t>
   </si>
   <si>
     <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
   </si>
   <si>
     <t>NC</t>
@@ -1091,7 +1091,7 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
         <v>5</v>
@@ -1106,7 +1106,7 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
         <v>6</v>
@@ -1124,7 +1124,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1168,7 +1168,7 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>5</v>
@@ -1183,10 +1183,10 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>6</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1245,7 +1245,7 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>10</v>
@@ -1260,10 +1260,10 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>9</v>
@@ -1322,7 +1322,7 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>6</v>
@@ -1337,7 +1337,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1399,7 +1399,7 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -1414,10 +1414,10 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>8</v>
@@ -1432,7 +1432,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1476,7 +1476,7 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>8</v>
@@ -1491,7 +1491,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1509,7 +1509,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1553,7 +1553,7 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>10</v>
@@ -1568,7 +1568,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1630,7 +1630,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -1645,7 +1645,7 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1707,7 +1707,7 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>5</v>
@@ -1722,10 +1722,10 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -1740,7 +1740,7 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1784,7 +1784,7 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>10</v>
@@ -1799,7 +1799,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -1861,7 +1861,7 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
         <v>9</v>
@@ -1876,10 +1876,10 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>10</v>
@@ -1894,7 +1894,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1938,7 +1938,7 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
         <v>10</v>
@@ -1953,10 +1953,10 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -2015,7 +2015,7 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>6</v>
@@ -2030,7 +2030,7 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>7</v>
@@ -2048,7 +2048,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2092,7 +2092,7 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
         <v>5</v>
@@ -2107,10 +2107,10 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -2169,7 +2169,7 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>10</v>
@@ -2184,7 +2184,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -2246,7 +2246,7 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
         <v>10</v>
@@ -2261,10 +2261,10 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>10</v>
@@ -2323,7 +2323,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>8</v>
@@ -2338,10 +2338,10 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2400,7 +2400,7 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -2415,7 +2415,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>6</v>
@@ -2433,7 +2433,7 @@
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2477,7 +2477,7 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>10</v>
@@ -2492,7 +2492,7 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>7</v>
@@ -2554,7 +2554,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>10</v>
@@ -2569,7 +2569,7 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -2631,7 +2631,7 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
         <v>10</v>
@@ -2646,7 +2646,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>7</v>
@@ -2664,7 +2664,7 @@
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2708,7 +2708,7 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
         <v>5</v>
@@ -2723,7 +2723,7 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T25">
         <v>6</v>
@@ -2785,7 +2785,7 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
         <v>10</v>
@@ -2800,7 +2800,7 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>8</v>
@@ -2818,7 +2818,7 @@
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2862,7 +2862,7 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
         <v>10</v>
@@ -2877,7 +2877,7 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -2939,7 +2939,7 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>10</v>
@@ -2954,7 +2954,7 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -3016,7 +3016,7 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>7</v>
@@ -3031,7 +3031,7 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
         <v>8</v>
@@ -3093,7 +3093,7 @@
         <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
         <v>5</v>
@@ -3108,7 +3108,7 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T30">
         <v>6</v>
@@ -3170,7 +3170,7 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O31">
         <v>5</v>
@@ -3185,7 +3185,7 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T31">
         <v>5</v>
@@ -3247,7 +3247,7 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
         <v>10</v>
@@ -3262,10 +3262,10 @@
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>10</v>
@@ -3280,7 +3280,7 @@
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3324,7 +3324,7 @@
         <v>5</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>5</v>
@@ -3339,10 +3339,10 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U33">
         <v>6</v>
@@ -3401,7 +3401,7 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
         <v>8</v>
@@ -3416,7 +3416,7 @@
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>9</v>
@@ -3478,7 +3478,7 @@
         <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O35">
         <v>7</v>
@@ -3493,7 +3493,7 @@
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T35">
         <v>6</v>
@@ -3555,7 +3555,7 @@
         <v>7</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O36">
         <v>8</v>
@@ -3570,10 +3570,10 @@
         <v>-1</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U36">
         <v>7</v>
@@ -3632,7 +3632,7 @@
         <v>6</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>5</v>
@@ -3647,10 +3647,10 @@
         <v>-1</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U37">
         <v>8</v>
@@ -3709,7 +3709,7 @@
         <v>5</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O38">
         <v>5</v>
@@ -3724,7 +3724,7 @@
         <v>-1</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T38">
         <v>6</v>
@@ -3786,7 +3786,7 @@
         <v>5</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O39">
         <v>8</v>
@@ -3801,10 +3801,10 @@
         <v>-1</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U39">
         <v>9</v>
@@ -3863,7 +3863,7 @@
         <v>8</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O40">
         <v>10</v>
@@ -3878,7 +3878,7 @@
         <v>-1</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T40">
         <v>8</v>
@@ -3940,7 +3940,7 @@
         <v>6</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O41">
         <v>10</v>
@@ -3955,7 +3955,7 @@
         <v>-1</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T41">
         <v>7</v>
@@ -4017,7 +4017,7 @@
         <v>5</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O42">
         <v>5</v>
@@ -4032,7 +4032,7 @@
         <v>-1</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T42">
         <v>6</v>
@@ -4094,7 +4094,7 @@
         <v>9</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O43">
         <v>10</v>
@@ -4109,7 +4109,7 @@
         <v>-1</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T43">
         <v>8</v>
@@ -4171,7 +4171,7 @@
         <v>6</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O44">
         <v>9</v>
@@ -4186,7 +4186,7 @@
         <v>-1</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T44">
         <v>9</v>
@@ -4248,7 +4248,7 @@
         <v>10</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O45">
         <v>10</v>
@@ -4263,7 +4263,7 @@
         <v>-1</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T45">
         <v>10</v>
@@ -4325,7 +4325,7 @@
         <v>7</v>
       </c>
       <c r="N46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O46">
         <v>10</v>
@@ -4340,7 +4340,7 @@
         <v>-1</v>
       </c>
       <c r="S46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T46">
         <v>9</v>
@@ -4478,7 +4478,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -4487,19 +4487,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>76.73999999999999</v>
+        <v>86.05</v>
       </c>
       <c r="G4">
-        <v>23.26</v>
+        <v>13.95</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4510,7 +4510,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -4531,7 +4531,7 @@
         <v>13.95</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
@@ -4563,7 +4563,7 @@
         <v>4.65</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>69</v>
@@ -4583,19 +4583,19 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>95.34999999999999</v>
+        <v>97.67</v>
       </c>
       <c r="G7">
-        <v>4.65</v>
+        <v>2.33</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5407,7 +5407,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920126</v>
+        <v>22330051920244</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5462,22 +5462,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920126</v>
+        <v>22330051920244</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5485,16 +5485,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920244</v>
+        <v>22330051920346</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5508,16 +5508,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920244</v>
+        <v>22330051920346</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5531,16 +5531,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920346</v>
+        <v>22330051920247</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5554,16 +5554,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920346</v>
+        <v>22330051920247</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5577,16 +5577,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920247</v>
+        <v>22330051920144</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5600,16 +5600,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920247</v>
+        <v>22330051920144</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="D9" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -5623,22 +5623,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920144</v>
+        <v>22330051920343</v>
       </c>
       <c r="B10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" t="s">
         <v>109</v>
       </c>
-      <c r="C10" t="s">
-        <v>135</v>
-      </c>
       <c r="D10" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5646,16 +5646,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920144</v>
+        <v>22330051920342</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920124</v>
+        <v>22330051920126</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5692,22 +5692,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920343</v>
+        <v>22330051920131</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5715,22 +5715,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920342</v>
+        <v>22330051920348</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5738,22 +5738,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920125</v>
+        <v>22330051920138</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D15" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -5761,16 +5761,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920131</v>
+        <v>22330051920354</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="D16" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -5779,98 +5779,6 @@
         <v>65</v>
       </c>
       <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920132</v>
-      </c>
-      <c r="B17" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" t="s">
-        <v>152</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>66</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920348</v>
-      </c>
-      <c r="B18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" t="s">
-        <v>161</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>67</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920138</v>
-      </c>
-      <c r="B19" t="s">
-        <v>98</v>
-      </c>
-      <c r="C19" t="s">
-        <v>129</v>
-      </c>
-      <c r="D19" t="s">
-        <v>166</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>64</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920354</v>
-      </c>
-      <c r="B20" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" t="s">
-        <v>134</v>
-      </c>
-      <c r="D20" t="s">
-        <v>175</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>65</v>
-      </c>
-      <c r="G20">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EM - Estadisticos 20221.xlsx
+++ b/grupos/1EM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="184">
   <si>
     <t>Materia</t>
   </si>
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -1115,7 +1115,7 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -1174,7 +1174,7 @@
         <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -1192,7 +1192,7 @@
         <v>8</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -1251,7 +1251,7 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -1269,7 +1269,7 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1328,7 +1328,7 @@
         <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1346,7 +1346,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1405,7 +1405,7 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1482,7 +1482,7 @@
         <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1559,7 +1559,7 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1636,7 +1636,7 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1713,7 +1713,7 @@
         <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1790,7 +1790,7 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1867,7 +1867,7 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1885,7 +1885,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1944,7 +1944,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -1962,7 +1962,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -2021,7 +2021,7 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -2039,7 +2039,7 @@
         <v>7</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -2098,7 +2098,7 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -2116,7 +2116,7 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -2175,7 +2175,7 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -2252,7 +2252,7 @@
         <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2329,7 +2329,7 @@
         <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2406,7 +2406,7 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2424,7 +2424,7 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2483,7 +2483,7 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2560,7 +2560,7 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2637,7 +2637,7 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2714,7 +2714,7 @@
         <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2791,7 +2791,7 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -2809,7 +2809,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2868,7 +2868,7 @@
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -2945,7 +2945,7 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -3022,7 +3022,7 @@
         <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -3099,7 +3099,7 @@
         <v>5</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -3176,7 +3176,7 @@
         <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -3253,7 +3253,7 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -3330,7 +3330,7 @@
         <v>5</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3407,7 +3407,7 @@
         <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -3484,7 +3484,7 @@
         <v>7</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -3561,7 +3561,7 @@
         <v>8</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -3579,7 +3579,7 @@
         <v>7</v>
       </c>
       <c r="V36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -3638,7 +3638,7 @@
         <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -3656,7 +3656,7 @@
         <v>8</v>
       </c>
       <c r="V37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W37">
         <v>8</v>
@@ -3715,7 +3715,7 @@
         <v>5</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -3792,7 +3792,7 @@
         <v>8</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -3869,7 +3869,7 @@
         <v>10</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q40">
         <v>-1</v>
@@ -3887,7 +3887,7 @@
         <v>10</v>
       </c>
       <c r="V40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W40">
         <v>7</v>
@@ -3946,7 +3946,7 @@
         <v>10</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q41">
         <v>-1</v>
@@ -4023,7 +4023,7 @@
         <v>5</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q42">
         <v>-1</v>
@@ -4100,7 +4100,7 @@
         <v>10</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q43">
         <v>-1</v>
@@ -4118,7 +4118,7 @@
         <v>10</v>
       </c>
       <c r="V43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W43">
         <v>10</v>
@@ -4177,7 +4177,7 @@
         <v>9</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q44">
         <v>-1</v>
@@ -4254,7 +4254,7 @@
         <v>10</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q45">
         <v>-1</v>
@@ -4272,7 +4272,7 @@
         <v>10</v>
       </c>
       <c r="V45">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W45">
         <v>10</v>
@@ -4331,7 +4331,7 @@
         <v>10</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q46">
         <v>-1</v>
@@ -4349,7 +4349,7 @@
         <v>10</v>
       </c>
       <c r="V46">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W46">
         <v>7</v>
@@ -4455,19 +4455,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>74.42</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G3">
-        <v>25.58</v>
+        <v>18.6</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5407,7 +5407,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5485,16 +5485,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920346</v>
+        <v>22330051920247</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5508,16 +5508,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920346</v>
+        <v>22330051920247</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5531,22 +5531,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920247</v>
+        <v>22330051920343</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5554,16 +5554,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920247</v>
+        <v>22330051920342</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5577,22 +5577,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920144</v>
+        <v>22330051920126</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5600,16 +5600,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920144</v>
+        <v>22330051920346</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -5623,22 +5623,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920343</v>
+        <v>22330051920348</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5646,16 +5646,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920342</v>
+        <v>22330051920138</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="D11" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920126</v>
+        <v>22330051920354</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5692,93 +5692,24 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920131</v>
+        <v>22330051920144</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920348</v>
-      </c>
-      <c r="B14" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" t="s">
-        <v>161</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920138</v>
-      </c>
-      <c r="B15" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" t="s">
-        <v>129</v>
-      </c>
-      <c r="D15" t="s">
-        <v>166</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>64</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920354</v>
-      </c>
-      <c r="B16" t="s">
-        <v>107</v>
-      </c>
-      <c r="C16" t="s">
-        <v>134</v>
-      </c>
-      <c r="D16" t="s">
-        <v>175</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EM - Estadisticos 20221.xlsx
+++ b/grupos/1EM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="184">
   <si>
     <t>Materia</t>
   </si>
@@ -212,16 +212,16 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
     <t>Moreno Aroyo Anél</t>
@@ -1103,7 +1103,7 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
         <v>7</v>
@@ -1121,7 +1121,7 @@
         <v>7</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -1180,7 +1180,7 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>7</v>
@@ -1198,7 +1198,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -1257,7 +1257,7 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>6</v>
@@ -1275,7 +1275,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -1334,7 +1334,7 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
         <v>6</v>
@@ -1352,7 +1352,7 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1411,7 +1411,7 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
         <v>6</v>
@@ -1488,7 +1488,7 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>7</v>
@@ -1506,7 +1506,7 @@
         <v>6</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1565,7 +1565,7 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
         <v>9</v>
@@ -1642,7 +1642,7 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>10</v>
@@ -1719,7 +1719,7 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>6</v>
@@ -1737,7 +1737,7 @@
         <v>8</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1796,7 +1796,7 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>9</v>
@@ -1873,7 +1873,7 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>8</v>
@@ -1950,7 +1950,7 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>7</v>
@@ -2027,7 +2027,7 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
         <v>7</v>
@@ -2104,7 +2104,7 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>6</v>
@@ -2181,7 +2181,7 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>10</v>
@@ -2258,7 +2258,7 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>9</v>
@@ -2335,7 +2335,7 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
         <v>6</v>
@@ -2353,7 +2353,7 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2412,7 +2412,7 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>7</v>
@@ -2430,7 +2430,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2489,7 +2489,7 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
         <v>6</v>
@@ -2507,7 +2507,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -2566,7 +2566,7 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>10</v>
@@ -2643,7 +2643,7 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
         <v>10</v>
@@ -2661,7 +2661,7 @@
         <v>5</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2720,7 +2720,7 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
         <v>5</v>
@@ -2738,7 +2738,7 @@
         <v>9</v>
       </c>
       <c r="X25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y25">
         <v>5</v>
@@ -2797,7 +2797,7 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>7</v>
@@ -2874,7 +2874,7 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
         <v>10</v>
@@ -2951,7 +2951,7 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>9</v>
@@ -3028,7 +3028,7 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
         <v>6</v>
@@ -3046,7 +3046,7 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -3105,7 +3105,7 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S30">
         <v>5</v>
@@ -3182,7 +3182,7 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S31">
         <v>5</v>
@@ -3259,7 +3259,7 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>9</v>
@@ -3277,7 +3277,7 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>8</v>
@@ -3336,7 +3336,7 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S33">
         <v>5</v>
@@ -3413,7 +3413,7 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
         <v>7</v>
@@ -3490,7 +3490,7 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
         <v>5</v>
@@ -3508,7 +3508,7 @@
         <v>5</v>
       </c>
       <c r="X35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y35">
         <v>5</v>
@@ -3567,7 +3567,7 @@
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S36">
         <v>7</v>
@@ -3585,7 +3585,7 @@
         <v>7</v>
       </c>
       <c r="X36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S37">
         <v>7</v>
@@ -3721,7 +3721,7 @@
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S38">
         <v>6</v>
@@ -3739,7 +3739,7 @@
         <v>8</v>
       </c>
       <c r="X38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y38">
         <v>6</v>
@@ -3798,7 +3798,7 @@
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S39">
         <v>7</v>
@@ -3816,7 +3816,7 @@
         <v>9</v>
       </c>
       <c r="X39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y39">
         <v>7</v>
@@ -3875,7 +3875,7 @@
         <v>-1</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S40">
         <v>8</v>
@@ -3893,7 +3893,7 @@
         <v>7</v>
       </c>
       <c r="X40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y40">
         <v>7</v>
@@ -3952,7 +3952,7 @@
         <v>-1</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S41">
         <v>6</v>
@@ -3970,7 +3970,7 @@
         <v>8</v>
       </c>
       <c r="X41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y41">
         <v>7</v>
@@ -4029,7 +4029,7 @@
         <v>-1</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S42">
         <v>5</v>
@@ -4106,7 +4106,7 @@
         <v>-1</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S43">
         <v>8</v>
@@ -4183,7 +4183,7 @@
         <v>-1</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S44">
         <v>6</v>
@@ -4260,7 +4260,7 @@
         <v>-1</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S45">
         <v>10</v>
@@ -4337,7 +4337,7 @@
         <v>-1</v>
       </c>
       <c r="R46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S46">
         <v>6</v>
@@ -4355,7 +4355,7 @@
         <v>7</v>
       </c>
       <c r="X46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y46">
         <v>7</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -4423,19 +4423,19 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>67.44</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G2">
-        <v>32.56</v>
+        <v>18.6</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4446,7 +4446,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -4455,19 +4455,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>81.40000000000001</v>
+        <v>86.05</v>
       </c>
       <c r="G3">
-        <v>18.6</v>
+        <v>13.95</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4478,7 +4478,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -4499,7 +4499,7 @@
         <v>13.95</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4510,7 +4510,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -4519,16 +4519,16 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>86.05</v>
+        <v>90.7</v>
       </c>
       <c r="G5">
-        <v>13.95</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H5">
         <v>7</v>
@@ -5407,7 +5407,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920244</v>
+        <v>22330051920136</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5462,22 +5462,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920244</v>
+        <v>22330051920136</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5485,19 +5485,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920247</v>
+        <v>22330051920141</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>65</v>
@@ -5508,22 +5508,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920247</v>
+        <v>22330051920141</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="D5" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5531,19 +5531,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920343</v>
+        <v>22330051920244</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>64</v>
@@ -5554,19 +5554,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920342</v>
+        <v>22330051920247</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>64</v>
@@ -5577,22 +5577,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920126</v>
+        <v>22330051920348</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5600,116 +5600,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920346</v>
+        <v>22330051920354</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
         <v>64</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920348</v>
-      </c>
-      <c r="B10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" t="s">
-        <v>161</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920138</v>
-      </c>
-      <c r="B11" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D11" t="s">
-        <v>166</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920354</v>
-      </c>
-      <c r="B12" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" t="s">
-        <v>134</v>
-      </c>
-      <c r="D12" t="s">
-        <v>175</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920144</v>
-      </c>
-      <c r="B13" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" t="s">
-        <v>135</v>
-      </c>
-      <c r="D13" t="s">
-        <v>177</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EM - Estadisticos 20221.xlsx
+++ b/grupos/1EM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="184">
   <si>
     <t>Materia</t>
   </si>
@@ -215,10 +215,10 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
     <t>Herrera Serrano Mayra Iliana</t>
@@ -1100,7 +1100,7 @@
         <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>9</v>
@@ -1118,7 +1118,7 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -1177,7 +1177,7 @@
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>10</v>
@@ -1195,7 +1195,7 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1254,7 +1254,7 @@
         <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>7</v>
@@ -1272,7 +1272,7 @@
         <v>6</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>6</v>
@@ -1331,7 +1331,7 @@
         <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>7</v>
@@ -1349,7 +1349,7 @@
         <v>6</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1408,7 +1408,7 @@
         <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>8</v>
@@ -1485,7 +1485,7 @@
         <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>8</v>
@@ -1503,7 +1503,7 @@
         <v>6</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>6</v>
@@ -1562,7 +1562,7 @@
         <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>8</v>
@@ -1639,7 +1639,7 @@
         <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>10</v>
@@ -1716,7 +1716,7 @@
         <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
         <v>9</v>
@@ -1793,7 +1793,7 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>7</v>
@@ -1811,7 +1811,7 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>9</v>
@@ -1947,7 +1947,7 @@
         <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>9</v>
@@ -1965,7 +1965,7 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -2024,7 +2024,7 @@
         <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
         <v>6</v>
@@ -2101,7 +2101,7 @@
         <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
         <v>8</v>
@@ -2119,7 +2119,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -2178,7 +2178,7 @@
         <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>10</v>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>10</v>
@@ -2332,7 +2332,7 @@
         <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
         <v>8</v>
@@ -2409,7 +2409,7 @@
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
         <v>7</v>
@@ -2427,7 +2427,7 @@
         <v>6</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2486,7 +2486,7 @@
         <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>7</v>
@@ -2504,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2563,7 +2563,7 @@
         <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>10</v>
@@ -2640,7 +2640,7 @@
         <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
         <v>9</v>
@@ -2658,7 +2658,7 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -2717,7 +2717,7 @@
         <v>5</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>7</v>
@@ -2794,7 +2794,7 @@
         <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>9</v>
@@ -2871,7 +2871,7 @@
         <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>9</v>
@@ -2948,7 +2948,7 @@
         <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>10</v>
@@ -3025,7 +3025,7 @@
         <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <v>8</v>
@@ -3102,7 +3102,7 @@
         <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R30">
         <v>5</v>
@@ -3179,7 +3179,7 @@
         <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R31">
         <v>5</v>
@@ -3256,7 +3256,7 @@
         <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>10</v>
@@ -3333,7 +3333,7 @@
         <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
         <v>5</v>
@@ -3410,7 +3410,7 @@
         <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
         <v>9</v>
@@ -3487,7 +3487,7 @@
         <v>7</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>8</v>
@@ -3505,7 +3505,7 @@
         <v>7</v>
       </c>
       <c r="W35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>6</v>
@@ -3564,7 +3564,7 @@
         <v>6</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>8</v>
@@ -3582,7 +3582,7 @@
         <v>6</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>7</v>
@@ -3641,7 +3641,7 @@
         <v>6</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
         <v>7</v>
@@ -3718,7 +3718,7 @@
         <v>5</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
         <v>8</v>
@@ -3736,7 +3736,7 @@
         <v>5</v>
       </c>
       <c r="W38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X38">
         <v>7</v>
@@ -3795,7 +3795,7 @@
         <v>8</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R39">
         <v>8</v>
@@ -3813,7 +3813,7 @@
         <v>8</v>
       </c>
       <c r="W39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X39">
         <v>7</v>
@@ -3872,7 +3872,7 @@
         <v>9</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
         <v>9</v>
@@ -3890,7 +3890,7 @@
         <v>7</v>
       </c>
       <c r="W40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>7</v>
@@ -3949,7 +3949,7 @@
         <v>6</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R41">
         <v>8</v>
@@ -3967,7 +3967,7 @@
         <v>6</v>
       </c>
       <c r="W41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X41">
         <v>7</v>
@@ -4026,7 +4026,7 @@
         <v>5</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R42">
         <v>5</v>
@@ -4103,7 +4103,7 @@
         <v>8</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R43">
         <v>8</v>
@@ -4121,7 +4121,7 @@
         <v>8</v>
       </c>
       <c r="W43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X43">
         <v>7</v>
@@ -4180,7 +4180,7 @@
         <v>8</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R44">
         <v>8</v>
@@ -4257,7 +4257,7 @@
         <v>9</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R45">
         <v>10</v>
@@ -4334,7 +4334,7 @@
         <v>7</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R46">
         <v>8</v>
@@ -4352,7 +4352,7 @@
         <v>7</v>
       </c>
       <c r="W46">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X46">
         <v>7</v>
@@ -4446,7 +4446,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -4467,7 +4467,7 @@
         <v>13.95</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4478,7 +4478,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -4487,19 +4487,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>86.05</v>
+        <v>88.37</v>
       </c>
       <c r="G4">
-        <v>13.95</v>
+        <v>11.63</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5407,7 +5407,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5439,16 +5439,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920136</v>
+        <v>22330051920247</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5462,19 +5462,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920136</v>
+        <v>22330051920247</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>66</v>
@@ -5485,22 +5485,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920141</v>
+        <v>22330051920136</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5508,22 +5508,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920141</v>
+        <v>22330051920136</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D5" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5554,22 +5554,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920247</v>
+        <v>22330051920141</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="D7" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5577,47 +5577,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920348</v>
+        <v>22330051920354</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="D8" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920354</v>
-      </c>
-      <c r="B9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" t="s">
-        <v>134</v>
-      </c>
-      <c r="D9" t="s">
-        <v>175</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>
